--- a/docs/SparshaGuard_paper_values.xlsx
+++ b/docs/SparshaGuard_paper_values.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Values from Papers'!$A$1:$J$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Values from Papers'!$A$1:$J$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J136"/>
+  <dimension ref="A1:J161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5016,70 +5016,68 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Body-to-body capacitance at 1 m (analytic)</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Two 1.8 m people</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Nath et al. 2021</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>M. Nath et al. (S. Sen group, Purdue) (2021). "Inter-Body Coupling in Electro-Quasistatic Human Body Communication: Theory and Analysis of Security and Interference Properties". Scientific Reports.</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2003.13329</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Agarwal &amp; Sahu 2010  —  Indian Journal of Plastic Surgery 43(1)</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="3" t="n"/>
-      <c r="I102" s="3" t="n"/>
-      <c r="J102" s="4" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Hand area (palmar, incl. fingers), men</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>146.5 ± 15.1</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>Indian adults 18–60, n = 150; Supports 40–80 cm² grab contact</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Agarwal &amp; Sahu 2010</t>
-        </is>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>P. Agarwal, S. Sahu (2010). "Determination of hand and palm area as a ratio of body surface area in Indian population". Indian Journal of Plastic Surgery 43(1).</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>https://www.thieme-connect.de/products/ejournals/pdf/10.1055/s-0039-1699403.pdf</t>
-        </is>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
-        <is>
-          <t>Yes (in model)</t>
-        </is>
-      </c>
+      <c r="B103" s="3" t="n"/>
+      <c r="C103" s="3" t="n"/>
+      <c r="D103" s="3" t="n"/>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="3" t="n"/>
+      <c r="H103" s="3" t="n"/>
+      <c r="I103" s="3" t="n"/>
+      <c r="J103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -5087,12 +5085,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Hand area (palmar, incl. fingers), women</t>
+          <t>Hand area (palmar, incl. fingers), men</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>132.4 ± 14.1</t>
+          <t>146.5 ± 15.1</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5102,7 +5100,7 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>n = 150</t>
+          <t>Indian adults 18–60, n = 150; Supports 40–80 cm² grab contact</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -5137,12 +5135,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Palm area, men</t>
+          <t>Hand area (palmar, incl. fingers), women</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>77.9 ± 10.3</t>
+          <t>132.4 ± 14.1</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5150,7 +5148,11 @@
           <t>cm²</t>
         </is>
       </c>
-      <c r="E105" s="5" t="inlineStr"/>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>n = 150</t>
+        </is>
+      </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
           <t>Agarwal &amp; Sahu 2010</t>
@@ -5173,7 +5175,7 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Background only</t>
+          <t>Yes (in model)</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5185,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Palm area, women</t>
+          <t>Palm area, men</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>73.7 ± 9.1</t>
+          <t>77.9 ± 10.3</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -5229,111 +5231,111 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
+          <t>Palm area, women</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>73.7 ± 9.1</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr"/>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Agarwal &amp; Sahu 2010</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>P. Agarwal, S. Sahu (2010). "Determination of hand and palm area as a ratio of body surface area in Indian population". Indian Journal of Plastic Surgery 43(1).</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>https://www.thieme-connect.de/products/ejournals/pdf/10.1055/s-0039-1699403.pdf</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
           <t>Hand as % of body surface area</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E107" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>Men and women</t>
         </is>
       </c>
-      <c r="F107" s="5" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>Agarwal &amp; Sahu 2010</t>
         </is>
       </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>P. Agarwal, S. Sahu (2010). "Determination of hand and palm area as a ratio of body surface area in Indian population". Indian Journal of Plastic Surgery 43(1).</t>
         </is>
       </c>
-      <c r="H107" s="5" t="inlineStr">
+      <c r="H108" s="5" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>https://www.thieme-connect.de/products/ejournals/pdf/10.1055/s-0039-1699403.pdf</t>
         </is>
       </c>
-      <c r="J107" s="5" t="inlineStr">
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>Background only</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>TI SNOA926 2015  —  Application report</t>
         </is>
       </c>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="3" t="n"/>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
-      <c r="J108" s="4" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Unshielded ground parasitic</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>&gt; 100 (can be)</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>pF</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr"/>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>TI SNOA926 2015</t>
-        </is>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Texas Instruments (2015). "Capacitive Sensing: Ins and Outs of Active Shielding (SNOA926A)". Application report.</t>
-        </is>
-      </c>
-      <c r="H109" s="5" t="inlineStr">
-        <is>
-          <t>Fig. 4</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>https://www.ti.com/lit/pdf/SNOA926</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
-        <is>
-          <t>Background only</t>
-        </is>
-      </c>
+      <c r="B109" s="3" t="n"/>
+      <c r="C109" s="3" t="n"/>
+      <c r="D109" s="3" t="n"/>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
+      <c r="J109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
@@ -5341,24 +5343,20 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Rejection of object behind sensor (3.6 cm)</t>
+          <t>Unshielded ground parasitic</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>50.9 / 61.1 / 76.3</t>
+          <t>&gt; 100 (can be)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>% reduction</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr">
-        <is>
-          <t>Same-size shield / 200% shield / ring + shield; Residual 24–49%</t>
-        </is>
-      </c>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="5" t="inlineStr">
         <is>
           <t>TI SNOA926 2015</t>
@@ -5371,7 +5369,7 @@
       </c>
       <c r="H110" s="5" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Fig. 4</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
@@ -5381,7 +5379,7 @@
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>Yes (in model)</t>
+          <t>Background only</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5389,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Rejection of object at side (1 cm)</t>
+          <t>Rejection of object behind sensor (3.6 cm)</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>37.2 / 70.6 / 77.0</t>
+          <t>50.9 / 61.1 / 76.3</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -5406,7 +5404,7 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Same three configurations; Residual 23–63%</t>
+          <t>Same-size shield / 200% shield / ring + shield; Residual 24–49%</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -5441,12 +5439,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Rejection of object at side (5 cm)</t>
+          <t>Rejection of object at side (1 cm)</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>34.2 / 64.6 / 75.0</t>
+          <t>37.2 / 70.6 / 77.0</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -5456,7 +5454,7 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Same three configurations</t>
+          <t>Same three configurations; Residual 23–63%</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
@@ -5481,7 +5479,7 @@
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>Background only</t>
+          <t>Yes (in model)</t>
         </is>
       </c>
     </row>
@@ -5491,115 +5489,115 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
+          <t>Rejection of object at side (5 cm)</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>34.2 / 64.6 / 75.0</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>% reduction</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Same three configurations</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>TI SNOA926 2015</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Texas Instruments (2015). "Capacitive Sensing: Ins and Outs of Active Shielding (SNOA926A)". Application report.</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ti.com/lit/pdf/SNOA926</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n">
+        <v>99</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
           <t>Loss of wanted sensitivity (top, 1 cm)</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C114" s="5" t="inlineStr">
         <is>
           <t>23.6 / 26.5 / 39.3</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>% reduction</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>Same three configurations; Shield also costs some signal</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F114" s="5" t="inlineStr">
         <is>
           <t>TI SNOA926 2015</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>Texas Instruments (2015). "Capacitive Sensing: Ins and Outs of Active Shielding (SNOA926A)". Application report.</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H114" s="5" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr">
+      <c r="I114" s="6" t="inlineStr">
         <is>
           <t>https://www.ti.com/lit/pdf/SNOA926</t>
         </is>
       </c>
-      <c r="J113" s="5" t="inlineStr">
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>Background only</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Hackaday ADC test  —  Hackaday.io</t>
         </is>
       </c>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="n"/>
-      <c r="I114" s="3" t="n"/>
-      <c r="J114" s="4" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>ESP32 built-in ADC fluctuation</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>~21.8</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>Unclear if std. dev. or p-p; ≈27 LSB at 3.3 V; Weak source</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>Hackaday ADC test</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>Hackaday.io project (n.d.). "ADC performance: Arduino vs ESP32 vs ADS1115". Hackaday.io.</t>
-        </is>
-      </c>
-      <c r="H115" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>https://hackaday.io/project/205380-adc-performance-arduino-vs-esp32-vs-ads1115</t>
-        </is>
-      </c>
-      <c r="J115" s="5" t="inlineStr">
-        <is>
-          <t>Yes (in model)</t>
-        </is>
-      </c>
+      <c r="B115" s="3" t="n"/>
+      <c r="C115" s="3" t="n"/>
+      <c r="D115" s="3" t="n"/>
+      <c r="E115" s="3" t="n"/>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="3" t="n"/>
+      <c r="H115" s="3" t="n"/>
+      <c r="I115" s="3" t="n"/>
+      <c r="J115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
@@ -5607,12 +5605,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Arduino ADC fluctuation</t>
+          <t>ESP32 built-in ADC fluctuation</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>~4.2</t>
+          <t>~21.8</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5620,7 +5618,11 @@
           <t>mV</t>
         </is>
       </c>
-      <c r="E116" s="5" t="inlineStr"/>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Unclear if std. dev. or p-p; ≈27 LSB at 3.3 V; Weak source</t>
+        </is>
+      </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
           <t>Hackaday ADC test</t>
@@ -5643,7 +5645,7 @@
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>Background only</t>
+          <t>Yes (in model)</t>
         </is>
       </c>
     </row>
@@ -5653,115 +5655,111 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
+          <t>Arduino ADC fluctuation</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>~4.2</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr"/>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Hackaday ADC test</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Hackaday.io project (n.d.). "ADC performance: Arduino vs ESP32 vs ADS1115". Hackaday.io.</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>https://hackaday.io/project/205380-adc-performance-arduino-vs-esp32-vs-ads1115</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
           <t>ADS1115 fluctuation</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>~2</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>mV</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>External ADC option</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>Hackaday ADC test</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>Hackaday.io project (n.d.). "ADC performance: Arduino vs ESP32 vs ADS1115". Hackaday.io.</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>https://hackaday.io/project/205380-adc-performance-arduino-vs-esp32-vs-ads1115</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>Background only</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Espressif ADC blog 2025  —  developer.espressif.com</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="n"/>
-      <c r="I118" s="3" t="n"/>
-      <c r="J118" s="4" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>ESP32 calibrated error</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>&lt; 30</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>mV</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>Accuracy, not noise</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>Espressif ADC blog 2025</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Espressif Systems (2025). "ADC performance (developer blog)". developer.espressif.com.</t>
-        </is>
-      </c>
-      <c r="H119" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>https://developer.espressif.com/blog/2025/08/adc-performance/</t>
-        </is>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t>Background only</t>
-        </is>
-      </c>
+      <c r="B119" s="3" t="n"/>
+      <c r="C119" s="3" t="n"/>
+      <c r="D119" s="3" t="n"/>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -5769,12 +5767,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>ESP32-S3 calibrated error</t>
+          <t>ESP32 calibrated error</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>−30 to 0</t>
+          <t>&lt; 30</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5782,7 +5780,11 @@
           <t>mV</t>
         </is>
       </c>
-      <c r="E120" s="5" t="inlineStr"/>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy, not noise</t>
+        </is>
+      </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
           <t>Espressif ADC blog 2025</t>
@@ -5815,24 +5817,20 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>ESP32 / ESP32-S3 DNL, INL</t>
+          <t>ESP32-S3 calibrated error</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>±7, ±12 / ±4, ±8</t>
+          <t>−30 to 0</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>LSB</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>Datasheet values</t>
-        </is>
-      </c>
+          <t>mV</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="5" t="inlineStr">
         <is>
           <t>Espressif ADC blog 2025</t>
@@ -5845,7 +5843,7 @@
       </c>
       <c r="H121" s="5" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Results</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
@@ -5865,20 +5863,24 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>ESP32 ADC sample rate</t>
+          <t>ESP32 / ESP32-S3 DNL, INL</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>200 k (RTC) / 2 M (DIG)</t>
+          <t>±7, ±12 / ±4, ±8</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>samples/s</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr"/>
+          <t>LSB</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Datasheet values</t>
+        </is>
+      </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
           <t>Espressif ADC blog 2025</t>
@@ -5911,115 +5913,111 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
+          <t>ESP32 ADC sample rate</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>200 k (RTC) / 2 M (DIG)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>samples/s</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr"/>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Espressif ADC blog 2025</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Espressif Systems (2025). "ADC performance (developer blog)". developer.espressif.com.</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>https://developer.espressif.com/blog/2025/08/adc-performance/</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
           <t>Noise advice</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>100 nF on ADC input; multisampling</t>
         </is>
       </c>
-      <c r="D123" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E123" s="5" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>No figures given</t>
         </is>
       </c>
-      <c r="F123" s="5" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
         <is>
           <t>Espressif ADC blog 2025</t>
         </is>
       </c>
-      <c r="G123" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>Espressif Systems (2025). "ADC performance (developer blog)". developer.espressif.com.</t>
         </is>
       </c>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="H124" s="5" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="I123" s="6" t="inlineStr">
+      <c r="I124" s="6" t="inlineStr">
         <is>
           <t>https://developer.espressif.com/blog/2025/08/adc-performance/</t>
         </is>
       </c>
-      <c r="J123" s="5" t="inlineStr">
+      <c r="J124" s="5" t="inlineStr">
         <is>
           <t>Background only</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Desco ESD table  —  descoindustries.com</t>
         </is>
       </c>
-      <c r="B124" s="3" t="n"/>
-      <c r="C124" s="3" t="n"/>
-      <c r="D124" s="3" t="n"/>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="4" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Body voltage, walking on vinyl floor</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>250 – 12,000</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>65-90% / 10-20% relative humidity</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>Desco ESD table</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Desco Industries (n.d.). "Typical Electrostatic Voltages". descoindustries.com.</t>
-        </is>
-      </c>
-      <c r="H125" s="5" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>https://www.descoindustries.com/AboutESD/Voltage.aspx</t>
-        </is>
-      </c>
-      <c r="J125" s="5" t="inlineStr">
-        <is>
-          <t>Whole-body study (doc)</t>
-        </is>
-      </c>
+      <c r="B125" s="3" t="n"/>
+      <c r="C125" s="3" t="n"/>
+      <c r="D125" s="3" t="n"/>
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
@@ -6027,405 +6025,1350 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
+          <t>Body voltage, walking on vinyl floor</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>250 – 12,000</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>65-90% / 10-20% relative humidity</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Desco ESD table</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Desco Industries (n.d.). "Typical Electrostatic Voltages". descoindustries.com.</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.descoindustries.com/AboutESD/Voltage.aspx</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>Whole-body study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>109</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
           <t>Body voltage, walking on carpet</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C127" s="5" t="inlineStr">
         <is>
           <t>1,500 – 35,000</t>
         </is>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E126" s="5" t="inlineStr">
+      <c r="E127" s="5" t="inlineStr">
         <is>
           <t>65-90% / 10-20% relative humidity</t>
         </is>
       </c>
-      <c r="F126" s="5" t="inlineStr">
+      <c r="F127" s="5" t="inlineStr">
         <is>
           <t>Desco ESD table</t>
         </is>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>Desco Industries (n.d.). "Typical Electrostatic Voltages". descoindustries.com.</t>
         </is>
       </c>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="I126" s="6" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>https://www.descoindustries.com/AboutESD/Voltage.aspx</t>
         </is>
       </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Jonassen (walking)  —  In Compliance Magazine</t>
         </is>
       </c>
-      <c r="B127" s="3" t="n"/>
-      <c r="C127" s="3" t="n"/>
-      <c r="D127" s="3" t="n"/>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="4" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="3" t="n"/>
+      <c r="C128" s="3" t="n"/>
+      <c r="D128" s="3" t="n"/>
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>Body voltage from walking on vinyl (measured)</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>up to ~3,500</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>Insulating floor</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>Jonassen (walking)</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>N. Jonassen (n.d.). "Charging by Walking (Mr. Static column)". In Compliance Magazine.</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="I128" s="6" t="inlineStr">
+      <c r="I129" s="6" t="inlineStr">
         <is>
           <t>https://incompliancemag.com/charging-by-walking/</t>
         </is>
       </c>
-      <c r="J128" s="5" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Bian et al. 2019  —  IEEE PerCom Workshops</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n"/>
-      <c r="C129" s="3" t="n"/>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="3" t="n"/>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
+          <t>Peak walking voltage formula</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>V_max = R · n · Δq</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>R to ground, n steps per second, Δq charge per step</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Jonassen (walking)</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>N. Jonassen (n.d.). "Charging by Walking (Mr. Static column)". In Compliance Magazine.</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Body resistance to ground from initial decay</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>≈ 2 × 10^10</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Walking test, decay after stopping</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Jonassen (walking)</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>N. Jonassen (n.d.). "Charging by Walking (Mr. Static column)". In Compliance Magazine.</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Bian et al. 2019  —  IEEE PerCom Workshops</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n"/>
+      <c r="C132" s="3" t="n"/>
+      <c r="D132" s="3" t="n"/>
+      <c r="E132" s="3" t="n"/>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
           <t>Wrist passive field sensor sensitivity</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>microvolt-level</t>
         </is>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E130" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>Wrist-worn, passive; Qualitative</t>
         </is>
       </c>
-      <c r="F130" s="5" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>Bian et al. 2019</t>
         </is>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>S. Bian, V. F. Rey, J. Younas, P. Lukowicz (2019). "Wrist-Worn Capacitive Sensor for Activity and Physical Collaboration Recognition". IEEE PerCom Workshops.</t>
         </is>
       </c>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="I130" s="6" t="inlineStr">
+      <c r="I133" s="6" t="inlineStr">
         <is>
           <t>https://dfki.de/web/forschung/projekte-publikationen/publikation/10312</t>
         </is>
       </c>
-      <c r="J130" s="5" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Bian, Liu, Lukowicz 2025  —  arXiv:2507.13520</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n"/>
-      <c r="C131" s="3" t="n"/>
-      <c r="D131" s="3" t="n"/>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="4" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B134" s="3" t="n"/>
+      <c r="C134" s="3" t="n"/>
+      <c r="D134" s="3" t="n"/>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
         <is>
           <t>ProxiBand: approaching person detected (TPR)</t>
         </is>
       </c>
-      <c r="C132" s="5" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>74.3 / 46</t>
         </is>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E132" s="5" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>Indoor / outdoor</t>
         </is>
       </c>
-      <c r="F132" s="5" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
         <is>
           <t>Bian, Liu, Lukowicz 2025</t>
         </is>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>S. Bian, M. Liu, P. Lukowicz (2025). "Passive Body-Area Electrostatic Field (Human Body Capacitance) for Ubiquitous Computing". arXiv:2507.13520.</t>
         </is>
       </c>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>Overview text</t>
         </is>
       </c>
-      <c r="I132" s="6" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>https://arxiv.org/html/2507.13520v1</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
+      <c r="J135" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Kurita 2016  —  Electrostatics Joint Conference</t>
         </is>
       </c>
-      <c r="B133" s="3" t="n"/>
-      <c r="C133" s="3" t="n"/>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="3" t="n"/>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="3" t="n"/>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
-      <c r="J133" s="4" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B136" s="3" t="n"/>
+      <c r="C136" s="3" t="n"/>
+      <c r="D136" s="3" t="n"/>
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
         <is>
           <t>Contact moment from electrostatic induction current</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C137" s="5" t="inlineStr">
         <is>
           <t>detected</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E137" s="5" t="inlineStr">
         <is>
           <t>Contact electrification; Qualitative</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F137" s="5" t="inlineStr">
         <is>
           <t>Kurita 2016</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G137" s="5" t="inlineStr">
         <is>
           <t>K. Kurita (2016). "Detection method for contact electrification based on electrostatic induction". Electrostatics Joint Conference.</t>
         </is>
       </c>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="I134" s="6" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>https://electrostatics.org/wp-content/uploads/2023/08/G12.pdf</t>
         </is>
       </c>
-      <c r="J134" s="5" t="inlineStr">
+      <c r="J137" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Elfekey et al. 2016  —  Sensors 16(12):2049</t>
         </is>
       </c>
-      <c r="B135" s="3" t="n"/>
-      <c r="C135" s="3" t="n"/>
-      <c r="D135" s="3" t="n"/>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="4" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B138" s="3" t="n"/>
+      <c r="C138" s="3" t="n"/>
+      <c r="D138" s="3" t="n"/>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
         <is>
           <t>Touch sensing from induced 50 Hz field on body</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C139" s="5" t="inlineStr">
         <is>
           <t>demonstrated</t>
         </is>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E136" s="5" t="inlineStr">
+      <c r="E139" s="5" t="inlineStr">
         <is>
           <t>Mains ELF field; Qualitative</t>
         </is>
       </c>
-      <c r="F136" s="5" t="inlineStr">
+      <c r="F139" s="5" t="inlineStr">
         <is>
           <t>Elfekey et al. 2016</t>
         </is>
       </c>
-      <c r="G136" s="5" t="inlineStr">
+      <c r="G139" s="5" t="inlineStr">
         <is>
           <t>H. Elfekey, H. A. Bastawrous, S. Okamoto (2016). "A Touch Sensing Technique Using the Effects of Extremely Low Frequency Fields on the Human Body". Sensors 16(12):2049.</t>
         </is>
       </c>
-      <c r="H136" s="5" t="inlineStr">
+      <c r="H139" s="5" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I139" s="6" t="inlineStr">
         <is>
           <t>https://doi.org/10.3390/s16122049</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
+      <c r="J139" s="5" t="inlineStr">
         <is>
           <t>Whole-body study (doc)</t>
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Hum at the controller input, touching vs not touching</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>&gt; 4 / &lt; 0.5</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Their sensing circuit, indoor mains field; Circuit-specific levels</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Elfekey et al. 2016</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>H. Elfekey, H. A. Bastawrous, S. Okamoto (2016). "A Touch Sensing Technique Using the Effects of Extremely Low Frequency Fields on the Human Body". Sensors 16(12):2049.</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s16122049</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GKVK Bengaluru weather normals  —  uasbangalore.edu.in</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n"/>
+      <c r="C141" s="3" t="n"/>
+      <c r="D141" s="3" t="n"/>
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Relative humidity at 08:30, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>85 – 89</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Monthly means, GKVK station</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>GKVK Bengaluru weather normals</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>University of Agricultural Sciences, Bangalore (GKVK agro-meteorological observatory) (n.d.). "Monthly weather normals, GKVK, Bengaluru". uasbangalore.edu.in.</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>https://uasbangalore.edu.in/images/Agrometerology/pdf/gkvk-monthly-weather-normals-2011-2020-converted.pdf</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="n">
+        <v>119</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Relative humidity at 17:30, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>37 – 58</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Monthly means (37 % Mar–Apr, 57–58 % Jul–Aug)</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>GKVK Bengaluru weather normals</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>University of Agricultural Sciences, Bangalore (GKVK agro-meteorological observatory) (n.d.). "Monthly weather normals, GKVK, Bengaluru". uasbangalore.edu.in.</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>https://uasbangalore.edu.in/images/Agrometerology/pdf/gkvk-monthly-weather-normals-2011-2020-converted.pdf</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Annual mean relative humidity at 17:30, Bengaluru</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>GKVK station</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>GKVK Bengaluru weather normals</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>University of Agricultural Sciences, Bangalore (GKVK agro-meteorological observatory) (n.d.). "Monthly weather normals, GKVK, Bengaluru". uasbangalore.edu.in.</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>https://uasbangalore.edu.in/images/Agrometerology/pdf/gkvk-monthly-weather-normals-2011-2020-converted.pdf</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>Fusion study (doc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>IPC ESD resource (ANSI/ESD S20.20)  —  electronics.org</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n"/>
+      <c r="C145" s="3" t="n"/>
+      <c r="D145" s="3" t="n"/>
+      <c r="E145" s="3" t="n"/>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="3" t="n"/>
+      <c r="H145" s="3" t="n"/>
+      <c r="I145" s="3" t="n"/>
+      <c r="J145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Person-footwear-floor path limit in ESD areas</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>&lt; 1.0 × 10^9</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>ANSI/ESD S20.20; Ordinary shoes are far above this</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>IPC ESD resource (ANSI/ESD S20.20)</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>IPC (Electronics.org) technical resource (n.d.). "Electrostatic Discharge (ESD), Factory Issues, Measurement Methods". electronics.org.</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.electronics.org/system/files/technical_resource/E15&amp;S22_02.pdf</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>ESD footwear resistance, low end</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>≈ 5 × 10^5</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>Commercial ESD footwear</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>IPC ESD resource (ANSI/ESD S20.20)</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>IPC (Electronics.org) technical resource (n.d.). "Electrostatic Discharge (ESD), Factory Issues, Measurement Methods". electronics.org.</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>https://www.electronics.org/system/files/technical_resource/E15&amp;S22_02.pdf</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Bian et al. 2025 (collaborative)  —  arXiv:2501.06940</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n"/>
+      <c r="C148" s="3" t="n"/>
+      <c r="D148" s="3" t="n"/>
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="n"/>
+      <c r="I148" s="3" t="n"/>
+      <c r="J148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>123</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Gain from adding body capacitance to wrist accelerometer (collaborative activities)</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>+16</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>% F-score</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr">
+        <is>
+          <t>Collaborative activity recognition</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Bian et al. 2025 (collaborative)</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>S. Bian, P. Lukowicz et al. (2025). "Collaborative Human Activity Recognition with Passive Inter-Body Electrostatic Field". arXiv:2501.06940.</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2501.06940</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Bian et al. 2022 (leg motion)  —  Springer (book chapter)</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n"/>
+      <c r="C150" s="3" t="n"/>
+      <c r="D150" s="3" t="n"/>
+      <c r="E150" s="3" t="n"/>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="3" t="n"/>
+      <c r="H150" s="3" t="n"/>
+      <c r="I150" s="3" t="n"/>
+      <c r="J150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Wrist body-capacitance vs IMU, leg-motion activities (F-score)</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>0.89 vs 0.78</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Wrist-worn, leg-dominated activities</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Bian et al. 2022 (leg motion)</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>S. Bian et al. (2022). "Using Human Body Capacitance Sensing to Monitor Leg Motion Dominated Activities with a Wrist Worn Device". Springer (book chapter).</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/chapter/10.1007/978-981-19-0361-8_5</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Loeffler 2014  —  PLOS ONE 9(9):e106664</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n"/>
+      <c r="C152" s="3" t="n"/>
+      <c r="D152" s="3" t="n"/>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Wrist accelerometer event detection accuracy (gunshot recoil)</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>Hold-out set incl. confusable activities; Lab conditions</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Loeffler 2014</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>C. E. Loeffler (2014). "Detecting Gunshots Using Wearable Accelerometers". PLOS ONE 9(9):e106664.</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0106664</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Siirtola 2019  —  UbiComp/ISWC adjunct</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n"/>
+      <c r="C154" s="3" t="n"/>
+      <c r="D154" s="3" t="n"/>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Wrist-only stress detection, balanced accuracy</t>
+        </is>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>Empatica E4, WESAD, LDA</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Siirtola 2019</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>P. Siirtola (2019). "Continuous stress detection using the sensors of commercial smartwatch (WESAD, Empatica E4)". UbiComp/ISWC adjunct.</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2203.09669</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Schmidt et al. 2018 (WESAD)  —  ACM ICMI</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n"/>
+      <c r="C156" s="3" t="n"/>
+      <c r="D156" s="3" t="n"/>
+      <c r="E156" s="3" t="n"/>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="3" t="n"/>
+      <c r="H156" s="3" t="n"/>
+      <c r="I156" s="3" t="n"/>
+      <c r="J156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Stress vs non-stress accuracy (best, chest device)</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>WESAD; Chest, not wrist</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Schmidt et al. 2018 (WESAD)</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>P. Schmidt, A. Reiss, R. Duerichen, C. Marberger, K. Van Laerhoven (2018). "Introducing WESAD, a Multimodal Dataset for Wearable Stress and Affect Detection". ACM ICMI.</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>https://www.eti.uni-siegen.de/ubicomp/home/datasets/icmi18/</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Audio distress detection 2026  —  arXiv:2608.04176</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n"/>
+      <c r="C158" s="3" t="n"/>
+      <c r="D158" s="3" t="n"/>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="n"/>
+      <c r="H158" s="3" t="n"/>
+      <c r="I158" s="3" t="n"/>
+      <c r="J158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Scream stage false alarm rate, before / after context filter</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>≈ 10 / ≈ 1</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>Smartphone, daily audio; 1 % ≈ 15 min of false alarms per day</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Audio distress detection 2026</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>(authors as listed on arXiv) (2026). "Smartphone Audio Based Distress Detection". arXiv:2608.04176.</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2608.04176</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>US Pat. 10,950,112  —  USPTO</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n"/>
+      <c r="C160" s="3" t="n"/>
+      <c r="D160" s="3" t="n"/>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Acceptable false-alarm budget for wrist detectors</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>≈ 1</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>per user per day</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Stated as technically reasonable; many users find it too many; Patent text</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>US Pat. 10,950,112</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>US Patent 10,950,112 (n.d.). "Wrist fall detector based on arm direction". USPTO.</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>Background</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/10950112</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J136"/>
-  <mergeCells count="22">
+  <autoFilter ref="A1:J161"/>
+  <mergeCells count="31">
+    <mergeCell ref="A160:J160"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A135:J135"/>
-    <mergeCell ref="A131:J131"/>
-    <mergeCell ref="A102:J102"/>
+    <mergeCell ref="A141:J141"/>
+    <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A152:J152"/>
+    <mergeCell ref="A115:J115"/>
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A127:J127"/>
-    <mergeCell ref="A114:J114"/>
+    <mergeCell ref="A148:J148"/>
     <mergeCell ref="A73:J73"/>
     <mergeCell ref="A98:J98"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A138:J138"/>
+    <mergeCell ref="A103:J103"/>
+    <mergeCell ref="A132:J132"/>
     <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A124:J124"/>
+    <mergeCell ref="A119:J119"/>
     <mergeCell ref="A90:J90"/>
-    <mergeCell ref="A108:J108"/>
+    <mergeCell ref="A128:J128"/>
     <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A118:J118"/>
     <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A133:J133"/>
+    <mergeCell ref="A145:J145"/>
+    <mergeCell ref="A158:J158"/>
+    <mergeCell ref="A136:J136"/>
+    <mergeCell ref="A154:J154"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A129:J129"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId1"/>
@@ -6516,31 +7459,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6552,7 +7511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6796,7 +7755,7 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -6904,7 +7863,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6976,6 +7935,168 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>University of Agricultural Sciences, Bangalore (GKVK agro-meteorological observatory) (n.d.). "Monthly weather normals, GKVK, Bengaluru". uasbangalore.edu.in.</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>https://uasbangalore.edu.in/images/Agrometerology/pdf/gkvk-monthly-weather-normals-2011-2020-converted.pdf</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>IPC (Electronics.org) technical resource (n.d.). "Electrostatic Discharge (ESD), Factory Issues, Measurement Methods". electronics.org.</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>https://www.electronics.org/system/files/technical_resource/E15&amp;S22_02.pdf</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>S. Bian, P. Lukowicz et al. (2025). "Collaborative Human Activity Recognition with Passive Inter-Body Electrostatic Field". arXiv:2501.06940.</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2501.06940</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>S. Bian et al. (2022). "Using Human Body Capacitance Sensing to Monitor Leg Motion Dominated Activities with a Wrist Worn Device". Springer (book chapter).</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/chapter/10.1007/978-981-19-0361-8_5</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>C. E. Loeffler (2014). "Detecting Gunshots Using Wearable Accelerometers". PLOS ONE 9(9):e106664.</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>https://journals.plos.org/plosone/article?id=10.1371%2Fjournal.pone.0106664</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>P. Siirtola (2019). "Continuous stress detection using the sensors of commercial smartwatch (WESAD, Empatica E4)". UbiComp/ISWC adjunct.</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2203.09669</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>P. Schmidt, A. Reiss, R. Duerichen, C. Marberger, K. Van Laerhoven (2018). "Introducing WESAD, a Multimodal Dataset for Wearable Stress and Affect Detection". ACM ICMI.</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>https://www.eti.uni-siegen.de/ubicomp/home/datasets/icmi18/</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>(authors as listed on arXiv) (2026). "Smartphone Audio Based Distress Detection". arXiv:2608.04176.</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/pdf/2608.04176</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>US Patent 10,950,112 (n.d.). "Wrist fall detector based on arm direction". USPTO.</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>https://image-ppubs.uspto.gov/dirsearch-public/print/downloadPdf/10950112</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7003,6 +8124,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/SparshaGuard_paper_values.xlsx
+++ b/docs/SparshaGuard_paper_values.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Values from Papers'!$A$1:$J$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Values from Papers'!$A$1:$J$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J161"/>
+  <dimension ref="A1:J224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7335,39 +7335,2266 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016  —  IEEE Trans. Electromagnetic Compatibility 58(4)</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n"/>
+      <c r="C162" s="3" t="n"/>
+      <c r="D162" s="3" t="n"/>
+      <c r="E162" s="3" t="n"/>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="3" t="n"/>
+      <c r="H162" s="3" t="n"/>
+      <c r="I162" s="3" t="n"/>
+      <c r="J162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Body voltage, worst case (incl. walking)</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>&gt; ±20</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>22 °C, 5 % RH</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke (2016). "Effect of Human Activities and Environmental Conditions on Electrostatic Charging". IEEE Trans. Electromagnetic Compatibility 58(4).</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Body capacitance to ground on concrete vs wood-frame floor</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>120 vs 60</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>Same person; concrete gives about half the voltage</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke (2016). "Effect of Human Activities and Environmental Conditions on Electrostatic Charging". IEEE Trans. Electromagnetic Compatibility 58(4).</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Spread of body voltage from capacitance differences alone</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>±30</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr"/>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke (2016). "Effect of Human Activities and Environmental Conditions on Electrostatic Charging". IEEE Trans. Electromagnetic Compatibility 58(4).</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Time for body charge to fall to 100 V without ESD shoes/floor</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>1 – 30</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>With ESD shoes/floor: 0.5–6 s</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>Talebzadeh et al. 2016</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke (2016). "Effect of Human Activities and Environmental Conditions on Electrostatic Charging". IEEE Trans. Electromagnetic Compatibility 58(4).</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Kangas et al. 2015  —  Gerontology 61(1):61-68</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n"/>
+      <c r="C167" s="3" t="n"/>
+      <c r="D167" s="3" t="n"/>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+      <c r="H167" s="3" t="n"/>
+      <c r="I167" s="3" t="n"/>
+      <c r="J167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Fall-sensor false alarms in long-term use</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>0.049 (0.025 improved)</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>16 older adults, 15,500 h</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Kangas et al. 2015</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>M. Kangas, R. Korpelainen, I. Vikman, L. Nyberg, T. Jämsä (2015). "Sensitivity and false alarm rate of a fall sensor in long-term fall detection in the elderly". Gerontology 61(1):61-68.</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1159/000362720</t>
+        </is>
+      </c>
+      <c r="J168" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Tchuente et al. 2020  —  Sensors 20(21):6377</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n"/>
+      <c r="C169" s="3" t="n"/>
+      <c r="D169" s="3" t="n"/>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="3" t="n"/>
+      <c r="H169" s="3" t="n"/>
+      <c r="I169" s="3" t="n"/>
+      <c r="J169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Aggressive-movement classification, smartwatch</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>99.6 % accuracy, 98.4 % sensitivity</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>30 people, scripted punch/shove/slap; Scripted</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Tchuente et al. 2020</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>F. Tchuente, N. Baddour, E. D. Lemaire (2020). "Classification of Aggressive Movements Using Smartwatches". Sensors 20(21):6377.</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s20216377</t>
+        </is>
+      </c>
+      <c r="J170" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TI OPA350 datasheet  —  Datasheet</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n"/>
+      <c r="C171" s="3" t="n"/>
+      <c r="D171" s="3" t="n"/>
+      <c r="E171" s="3" t="n"/>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="3" t="n"/>
+      <c r="H171" s="3" t="n"/>
+      <c r="I171" s="3" t="n"/>
+      <c r="J171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n">
+        <v>136</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>OPA350 input capacitance</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>≈ 9</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>Typical</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>TI OPA350 datasheet</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>Texas Instruments (2015). "OPA350, OPA2350, OPA4350 high-speed single-supply rail-to-rail operational amplifiers (SBOS099D)". Datasheet.</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ti.com/lit/ds/symlink/opa350.pdf</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>ECN trace capacitance  —  Trade article</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="n"/>
+      <c r="H173" s="3" t="n"/>
+      <c r="I173" s="3" t="n"/>
+      <c r="J173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n">
+        <v>137</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>PCB trace capacitance</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>pF/cm</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>0.8 mm trace on 0.8 mm FR-4 over a plane</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>ECN trace capacitance</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>ECN / passive-components.eu (using TI figures) (n.d.). "A Plague of Parasites (PCB trace capacitance)". Trade article.</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>https://passive-components.eu/</t>
+        </is>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>SCS parylene data  —  Manufacturer technical data</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n"/>
+      <c r="C175" s="3" t="n"/>
+      <c r="D175" s="3" t="n"/>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="3" t="n"/>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="n">
+        <v>138</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Parylene relative permittivity, N / C</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>2.65 / 2.95–3.15</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>1 MHz (C: 3.15 at 60 Hz)</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>SCS parylene data</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>Specialty Coating Systems (n.d.). "Parylene Dielectric Properties". Manufacturer technical data.</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>https://scscoatings.com/</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Visuri et al. 2017  —  Proc. ACM CHI 2017, pp. 3569-3581</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n"/>
+      <c r="C177" s="3" t="n"/>
+      <c r="D177" s="3" t="n"/>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="3" t="n"/>
+      <c r="H177" s="3" t="n"/>
+      <c r="I177" s="3" t="n"/>
+      <c r="J177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="n">
+        <v>139</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>Smartwatch usage sessions</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>≈ 140</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>per day</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>307 users; about two-thirds are glances; 140/day secondary</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>Visuri et al. 2017</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>A. Visuri, Z. Sarsenbayeva, N. van Berkel, J. Goncalves, R. Rawassizadeh, V. Kostakos, D. Ferreira (2017). "Quantifying Sources and Types of Smartwatch Usage Sessions". Proc. ACM CHI 2017, pp. 3569-3581.</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>Abstract + news</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3025453.3025817</t>
+        </is>
+      </c>
+      <c r="J178" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Smartwatch sessions shorter than 5 s; mean session</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>half; ≈ 9 s</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="inlineStr"/>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Visuri et al. 2017</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>A. Visuri, Z. Sarsenbayeva, N. van Berkel, J. Goncalves, R. Rawassizadeh, V. Kostakos, D. Ferreira (2017). "Quantifying Sources and Types of Smartwatch Usage Sessions". Proc. ACM CHI 2017, pp. 3569-3581.</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>Abstract + news</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3025453.3025817</t>
+        </is>
+      </c>
+      <c r="J179" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Andrews et al. 2015  —  PLoS ONE 10(10):e0139004</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n"/>
+      <c r="C180" s="3" t="n"/>
+      <c r="D180" s="3" t="n"/>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="3" t="n"/>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Smartphone uses per day; total use</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>≈ 85; ≈ 5 h</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>23 adults, 2 weeks; more than half under 30 s; Secondary</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Andrews et al. 2015</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>S. Andrews, D. A. Ellis, H. Shaw, L. Piwek (2015). "Beyond Self-Report: Tools to Compare Estimated and Real-World Smartphone Use". PLoS ONE 10(10):e0139004.</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>Press release</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0139004</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Ficker 2005  —  J. Phys. D: Appl. Phys. 38(5):410-417</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n"/>
+      <c r="C182" s="3" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Body capacitance standing on both feet / on one foot</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>160 / 100</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>Vinyl tile; Secondary</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Ficker 2005</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>T. Ficker (2005). "Charging by walking". J. Phys. D: Appl. Phys. 38(5):410-417.</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>Summary article</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>Body resistance to ground on vinyl tile</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>≈ 10^11</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>Ω</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>Ficker 2005</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>T. Ficker (2005). "Charging by walking". J. Phys. D: Appl. Phys. 38(5):410-417.</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>Summary article</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J184" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Lifting a foot raises body voltage</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>8 – 12</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Walking on resistive floors; Secondary</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Ficker 2005</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>T. Ficker (2005). "Charging by walking". J. Phys. D: Appl. Phys. 38(5):410-417.</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="J185" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Tudor-Locke et al. 2012  —  Sports Medicine 42(5):381-398</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n"/>
+      <c r="C186" s="3" t="n"/>
+      <c r="D186" s="3" t="n"/>
+      <c r="E186" s="3" t="n"/>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="3" t="n"/>
+      <c r="H186" s="3" t="n"/>
+      <c r="I186" s="3" t="n"/>
+      <c r="J186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Walking cadence, women (normal lab walking)</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>96 – 138</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>steps/min</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>Across the lifespan</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Tudor-Locke et al. 2012</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>C. Tudor-Locke, H. Han, E. J. Aguiar, et al. (2012). "Using cadence to study free-living ambulatory activity". Sports Medicine 42(5):381-398.</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>https://strathprints.strath.ac.uk/42646/</t>
+        </is>
+      </c>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Neacsu et al. 2007  —  IMEKO TC4 Symposium, Iasi</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n"/>
+      <c r="C188" s="3" t="n"/>
+      <c r="D188" s="3" t="n"/>
+      <c r="E188" s="3" t="n"/>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="3" t="n"/>
+      <c r="H188" s="3" t="n"/>
+      <c r="I188" s="3" t="n"/>
+      <c r="J188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Change of body capacitance, sitting on a wooden chair vs standing</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>&lt; 10</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr"/>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>Neacsu et al. 2007</t>
+        </is>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>D. Neacsu, A. Salceanu, E. Lunca, V. David (2007). "Indirect Measurements on the Capacity in the Electrostatic HB Model". IMEKO TC4 Symposium, Iasi.</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>https://imeko.org/proceedings/indirect-measurements-on-the-capacity-in-the-electrostatic-hb-model</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>Measured human body capacitance, range</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>50 – 500</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E190" s="5" t="inlineStr"/>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Neacsu et al. 2007</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>D. Neacsu, A. Salceanu, E. Lunca, V. David (2007). "Indirect Measurements on the Capacity in the Electrostatic HB Model". IMEKO TC4 Symposium, Iasi.</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>https://imeko.org/proceedings/indirect-measurements-on-the-capacity-in-the-electrostatic-hb-model</t>
+        </is>
+      </c>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Body capacitance barefoot on 1 rubber carpet / on 4 carpets</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>295 / 116</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr"/>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Neacsu et al. 2007</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>D. Neacsu, A. Salceanu, E. Lunca, V. David (2007). "Indirect Measurements on the Capacity in the Electrostatic HB Model". IMEKO TC4 Symposium, Iasi.</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>Snippet</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>https://imeko.org/proceedings/indirect-measurements-on-the-capacity-in-the-electrostatic-hb-model</t>
+        </is>
+      </c>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Dawkins et al. 2022  —  J. Sports Sciences</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n"/>
+      <c r="C192" s="3" t="n"/>
+      <c r="D192" s="3" t="n"/>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="3" t="n"/>
+      <c r="H192" s="3" t="n"/>
+      <c r="I192" s="3" t="n"/>
+      <c r="J192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Wrist acceleration (ENMO), slow / normal / brisk walking</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>140 / 210 / 350</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>Adults 40–69, wrist, averaged; Averaged, not peaks</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Dawkins et al. 2022</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>N. P. Dawkins, T. Yates, et al. (2022). "Normative wrist-worn accelerometer values for self-paced walking and running: a walk in the park". J. Sports Sciences.</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/02640414.2021.1976491</t>
+        </is>
+      </c>
+      <c r="J193" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Walking recognition 2022  —  arXiv:2207.07443</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n"/>
+      <c r="C194" s="3" t="n"/>
+      <c r="D194" s="3" t="n"/>
+      <c r="E194" s="3" t="n"/>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="3" t="n"/>
+      <c r="H194" s="3" t="n"/>
+      <c r="I194" s="3" t="n"/>
+      <c r="J194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>Walking periodicity; wrist shows half the step rate</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>≈ 1.7</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>Pooled datasets</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>Walking recognition 2022</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>(authors as listed on arXiv) (2022). "A 'one-size-fits-most' walking recognition method for smartphones, smartwatches, and wearable accelerometers". arXiv:2207.07443.</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>Snippet</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2207.07443</t>
+        </is>
+      </c>
+      <c r="J195" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Public transport perturbation 2020  —  Z. Gerontol. Geriatr.</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n"/>
+      <c r="C196" s="3" t="n"/>
+      <c r="D196" s="3" t="n"/>
+      <c r="E196" s="3" t="n"/>
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="3" t="n"/>
+      <c r="H196" s="3" t="n"/>
+      <c r="I196" s="3" t="n"/>
+      <c r="J196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Bus acceleration from standstill / braking into a stop, maxima</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>3.37 / −3.12</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>12 days, sensor on a vertical bar</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>Public transport perturbation 2020</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>(authors not visible in the abstract) (2020). "Perturbation in public transport as a basic concept for perturbation-based balance training for fall prevention". Z. Gerontol. Geriatr..</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/journal/391</t>
+        </is>
+      </c>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>Tram acceleration / braking maxima</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>1.80 / −2.31</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>Same study</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>Public transport perturbation 2020</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>(authors not visible in the abstract) (2020). "Perturbation in public transport as a basic concept for perturbation-based balance training for fall prevention". Z. Gerontol. Geriatr..</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/journal/391</t>
+        </is>
+      </c>
+      <c r="J198" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Perry &amp; Burnfield 2010  —  SLACK Inc.</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n"/>
+      <c r="C199" s="3" t="n"/>
+      <c r="D199" s="3" t="n"/>
+      <c r="E199" s="3" t="n"/>
+      <c r="F199" s="3" t="n"/>
+      <c r="G199" s="3" t="n"/>
+      <c r="H199" s="3" t="n"/>
+      <c r="I199" s="3" t="n"/>
+      <c r="J199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Gait phases: double support / loading response / toe-off</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>0–10 % and 50–60 % / 0–10 % / 60 %</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>% of stride</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>Normal walking</t>
+        </is>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>Perry &amp; Burnfield 2010</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>J. Perry, J. M. Burnfield (2010). "Gait Analysis: Normal and Pathological Function, 2nd ed.". SLACK Inc..</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>Textbook</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>https://www.healio.com/books</t>
+        </is>
+      </c>
+      <c r="J200" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Krašna et al. 2021  —  Frontiers in Bioengineering and Biotechnology 9:680883</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n"/>
+      <c r="C201" s="3" t="n"/>
+      <c r="D201" s="3" t="n"/>
+      <c r="E201" s="3" t="n"/>
+      <c r="F201" s="3" t="n"/>
+      <c r="G201" s="3" t="n"/>
+      <c r="H201" s="3" t="n"/>
+      <c r="I201" s="3" t="n"/>
+      <c r="J201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Standing-passenger perturbation pulses tested</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>1.5 and 3.0 (acc.), 1.0 and 2.5 (braking)</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>m/s²</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>Sled tests, 24 volunteers</t>
+        </is>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>Krašna et al. 2021</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>S. Krašna, et al. (2021). "Human Response to Longitudinal Perturbations of Standing Passengers on Public Transport During Regular Operation". Frontiers in Bioengineering and Biotechnology 9:680883.</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fbioe.2021.680883</t>
+        </is>
+      </c>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Kwok et al. 2015  —  American Journal of Infection Control 43(2):112-114</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n"/>
+      <c r="C203" s="3" t="n"/>
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="3" t="n"/>
+      <c r="F203" s="3" t="n"/>
+      <c r="G203" s="3" t="n"/>
+      <c r="H203" s="3" t="n"/>
+      <c r="I203" s="3" t="n"/>
+      <c r="J203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Face touching</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>26 students in a lecture</t>
+        </is>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>Kwok et al. 2015</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>Y. L. A. Kwok, J. Gralton, M.-L. McLaws (2015). "Face touching: a frequent habit that has implications for hand hygiene". American Journal of Infection Control 43(2):112-114.</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ajic.2014.10.015</t>
+        </is>
+      </c>
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Mow et al. 2024  —  Proc. ICE Municipal Engineer</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n"/>
+      <c r="C205" s="3" t="n"/>
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="3" t="n"/>
+      <c r="F205" s="3" t="n"/>
+      <c r="G205" s="3" t="n"/>
+      <c r="H205" s="3" t="n"/>
+      <c r="I205" s="3" t="n"/>
+      <c r="J205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n">
+        <v>156</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Train-interior touches per passenger movement</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>0.07 – 0.57</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>touches</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>London Underground, 16,891 passengers</t>
+        </is>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>Mow et al. 2024</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>S. Mow, S. Seriani, T. Fujiyama (2024). "Where and how often do people touch train interiors? An investigation during the pandemic". Proc. ICE Municipal Engineer.</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>https://discovery.ucl.ac.uk/id/eprint/10199779/</t>
+        </is>
+      </c>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>BMRCL EIA  —  BMRCL / JICA</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n"/>
+      <c r="C207" s="3" t="n"/>
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="3" t="n"/>
+      <c r="F207" s="3" t="n"/>
+      <c r="G207" s="3" t="n"/>
+      <c r="H207" s="3" t="n"/>
+      <c r="I207" s="3" t="n"/>
+      <c r="J207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>Bengaluru Metro design loads (standing)</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>4 / 6 / 8</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>per m²</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>Normal / crush / dense crush</t>
+        </is>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>BMRCL EIA</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>Bangalore Metro Rail Corporation Ltd. (n.d.). "Environmental Impact Assessment (design passenger loads)". BMRCL / JICA.</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>https://www.jica.go.jp/</t>
+        </is>
+      </c>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>ISEC WP 437 (2019)  —  ISEC</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n"/>
+      <c r="C209" s="3" t="n"/>
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="3" t="n"/>
+      <c r="F209" s="3" t="n"/>
+      <c r="G209" s="3" t="n"/>
+      <c r="H209" s="3" t="n"/>
+      <c r="I209" s="3" t="n"/>
+      <c r="J209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>One-way commute in Bengaluru</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>10.84 km average</t>
+        </is>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>ISEC WP 437 (2019)</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>Institute for Social and Economic Change (2019). "Determinants of intra-urban mobility: a study of Bengaluru (Working Paper 437)". ISEC.</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/p/sch/wpaper/437.html</t>
+        </is>
+      </c>
+      <c r="J210" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Espressif ESP-FAQ  —  Espressif documentation</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n"/>
+      <c r="C211" s="3" t="n"/>
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="3" t="n"/>
+      <c r="F211" s="3" t="n"/>
+      <c r="G211" s="3" t="n"/>
+      <c r="H211" s="3" t="n"/>
+      <c r="I211" s="3" t="n"/>
+      <c r="J211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>ESP32 SAR ADC sample-and-hold capacitance</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>≈ 1</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr"/>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>Espressif ESP-FAQ</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>Espressif Systems (n.d.). "ESP-FAQ: ADC". Espressif documentation.</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>https://docs.espressif.com/projects/esp-faq/</t>
+        </is>
+      </c>
+      <c r="J212" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Step-to-Charge 2024  —  arXiv:2408.01927</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n"/>
+      <c r="C213" s="3" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="n"/>
+      <c r="F213" s="3" t="n"/>
+      <c r="G213" s="3" t="n"/>
+      <c r="H213" s="3" t="n"/>
+      <c r="I213" s="3" t="n"/>
+      <c r="J213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="5" t="n">
+        <v>160</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>Wearable floating ground to earth</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>≤ 1</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>pF</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>Wearable form factors</t>
+        </is>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Step-to-Charge 2024</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>(Sen group, Purdue) (2024). "Step-to-Charge (EQS body powering)". arXiv:2408.01927.</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.01927</t>
+        </is>
+      </c>
+      <c r="J214" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>IEC 61000-4-2  —  International standard</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n"/>
+      <c r="C215" s="3" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="n"/>
+      <c r="F215" s="3" t="n"/>
+      <c r="G215" s="3" t="n"/>
+      <c r="H215" s="3" t="n"/>
+      <c r="I215" s="3" t="n"/>
+      <c r="J215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>Human-body model (test standard)</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>150 pF, 330 Ω</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>Discharge time constant ≈ 50 ns; rise time 0.8 ns ±25 %</t>
+        </is>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>IEC 61000-4-2</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>IEC (2008). "IEC 61000-4-2: Electrostatic discharge immunity test". International standard.</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t>https://webstore.iec.ch/publication/4189</t>
+        </is>
+      </c>
+      <c r="J216" s="5" t="inlineStr">
+        <is>
+          <t>Yes (in model, Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Ramallah ELF survey  —  Journal article</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n"/>
+      <c r="C217" s="3" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="n"/>
+      <c r="F217" s="3" t="n"/>
+      <c r="G217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
+      <c r="I217" s="3" t="n"/>
+      <c r="J217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>Indoor 50 Hz electric field in homes, geometric mean</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>V/m</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>32 homes, log-normal</t>
+        </is>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>Ramallah ELF survey</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>(Al-Quds / An-Najah University) (n.d.). "Residential exposure to ELF electric and magnetic fields in the city of Ramallah-Palestine". Journal article.</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>https://dspace.alquds.edu/items/bc4377ca-bfb7-4375-ab1a-435c8e020c57/full</t>
+        </is>
+      </c>
+      <c r="J218" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Aziz et al. 2017  —  PLoS ONE 12(7):e0180318</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n"/>
+      <c r="C219" s="3" t="n"/>
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="3" t="n"/>
+      <c r="F219" s="3" t="n"/>
+      <c r="G219" s="3" t="n"/>
+      <c r="H219" s="3" t="n"/>
+      <c r="I219" s="3" t="n"/>
+      <c r="J219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Fall-detector false alarms, real-world</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>0 – 0.3</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>per hour</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>≈ 400 h, waist/sternum</t>
+        </is>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>Aziz et al. 2017</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>O. Aziz, et al. (2017). "Validation of accuracy of SVM-based fall detection system using real-world fall and non-fall datasets". PLoS ONE 12(7):e0180318.</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0180318</t>
+        </is>
+      </c>
+      <c r="J220" s="5" t="inlineStr">
+        <is>
+          <t>Accuracy benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Indraganti et al. 2014  —  Windsor Conference</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n"/>
+      <c r="C221" s="3" t="n"/>
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="3" t="n"/>
+      <c r="F221" s="3" t="n"/>
+      <c r="G221" s="3" t="n"/>
+      <c r="H221" s="3" t="n"/>
+      <c r="I221" s="3" t="n"/>
+      <c r="J221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Thermal insulation of a sari, by drape</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>0.62 – 0.94</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>clo</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>Manikin, ISO 9920</t>
+        </is>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>Indraganti et al. 2014</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>M. Indraganti, et al. (2014). "Thermal insulation of Indian clothing ensembles (sari, salwar-kurti)". Windsor Conference.</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>Abstract</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>https://architexturez.net/node/175314</t>
+        </is>
+      </c>
+      <c r="J222" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Majumdar et al. (Hyderabad)  —  Transportation Research Record</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n"/>
+      <c r="C223" s="3" t="n"/>
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="3" t="n"/>
+      <c r="F223" s="3" t="n"/>
+      <c r="G223" s="3" t="n"/>
+      <c r="H223" s="3" t="n"/>
+      <c r="I223" s="3" t="n"/>
+      <c r="J223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Physical harassment in public transport: touching / groping</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>58.8 / 53.2</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>% of victims</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>Hyderabad, 583 respondents; Secondary</t>
+        </is>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Majumdar et al. (Hyderabad)</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>B. B. Majumdar, et al. (BITS Pilani Hyderabad) (n.d.). "Harassment of women in public transport, Hyderabad". Transportation Research Record.</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/home/trr</t>
+        </is>
+      </c>
+      <c r="J224" s="5" t="inlineStr">
+        <is>
+          <t>Background only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J161"/>
-  <mergeCells count="31">
+  <autoFilter ref="A1:J224"/>
+  <mergeCells count="58">
+    <mergeCell ref="A203:J203"/>
     <mergeCell ref="A160:J160"/>
     <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A194:J194"/>
     <mergeCell ref="A141:J141"/>
+    <mergeCell ref="A219:J219"/>
     <mergeCell ref="A150:J150"/>
+    <mergeCell ref="A188:J188"/>
+    <mergeCell ref="A213:J213"/>
+    <mergeCell ref="A215:J215"/>
     <mergeCell ref="A109:J109"/>
+    <mergeCell ref="A180:J180"/>
     <mergeCell ref="A156:J156"/>
     <mergeCell ref="A125:J125"/>
+    <mergeCell ref="A171:J171"/>
+    <mergeCell ref="A209:J209"/>
     <mergeCell ref="A134:J134"/>
+    <mergeCell ref="A199:J199"/>
     <mergeCell ref="A152:J152"/>
     <mergeCell ref="A115:J115"/>
     <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A167:J167"/>
+    <mergeCell ref="A173:J173"/>
+    <mergeCell ref="A211:J211"/>
     <mergeCell ref="A148:J148"/>
+    <mergeCell ref="A186:J186"/>
     <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A201:J201"/>
+    <mergeCell ref="A182:J182"/>
     <mergeCell ref="A98:J98"/>
     <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A49:J49"/>
     <mergeCell ref="A138:J138"/>
+    <mergeCell ref="A207:J207"/>
     <mergeCell ref="A103:J103"/>
     <mergeCell ref="A132:J132"/>
     <mergeCell ref="A79:J79"/>
     <mergeCell ref="A119:J119"/>
+    <mergeCell ref="A162:J162"/>
+    <mergeCell ref="A196:J196"/>
+    <mergeCell ref="A205:J205"/>
+    <mergeCell ref="A221:J221"/>
+    <mergeCell ref="A177:J177"/>
     <mergeCell ref="A90:J90"/>
     <mergeCell ref="A128:J128"/>
     <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A217:J217"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="A145:J145"/>
     <mergeCell ref="A158:J158"/>
     <mergeCell ref="A136:J136"/>
     <mergeCell ref="A154:J154"/>
+    <mergeCell ref="A192:J192"/>
+    <mergeCell ref="A223:J223"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A175:J175"/>
     <mergeCell ref="A76:J76"/>
   </mergeCells>
   <hyperlinks>
@@ -7500,6 +9727,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I195" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7511,7 +9774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8097,6 +10360,492 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>A. Talebzadeh, M. Moradian, Y. Han, D. E. Swenson, D. Pommerenke (2016). "Effect of Human Activities and Environmental Conditions on Electrostatic Charging". IEEE Trans. Electromagnetic Compatibility 58(4).</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TEMC.2016.2575842</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>M. Kangas, R. Korpelainen, I. Vikman, L. Nyberg, T. Jämsä (2015). "Sensitivity and false alarm rate of a fall sensor in long-term fall detection in the elderly". Gerontology 61(1):61-68.</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1159/000362720</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>F. Tchuente, N. Baddour, E. D. Lemaire (2020). "Classification of Aggressive Movements Using Smartwatches". Sensors 20(21):6377.</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s20216377</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Texas Instruments (2015). "OPA350, OPA2350, OPA4350 high-speed single-supply rail-to-rail operational amplifiers (SBOS099D)". Datasheet.</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ti.com/lit/ds/symlink/opa350.pdf</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>ECN / passive-components.eu (using TI figures) (n.d.). "A Plague of Parasites (PCB trace capacitance)". Trade article.</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>https://passive-components.eu/</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Specialty Coating Systems (n.d.). "Parylene Dielectric Properties". Manufacturer technical data.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>https://scscoatings.com/</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>A. Visuri, Z. Sarsenbayeva, N. van Berkel, J. Goncalves, R. Rawassizadeh, V. Kostakos, D. Ferreira (2017). "Quantifying Sources and Types of Smartwatch Usage Sessions". Proc. ACM CHI 2017, pp. 3569-3581.</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1145/3025453.3025817</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>S. Andrews, D. A. Ellis, H. Shaw, L. Piwek (2015). "Beyond Self-Report: Tools to Compare Estimated and Real-World Smartphone Use". PLoS ONE 10(10):e0139004.</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0139004</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>T. Ficker (2005). "Charging by walking". J. Phys. D: Appl. Phys. 38(5):410-417.</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>https://incompliancemag.com/charging-by-walking/</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>C. Tudor-Locke, H. Han, E. J. Aguiar, et al. (2012). "Using cadence to study free-living ambulatory activity". Sports Medicine 42(5):381-398.</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>https://strathprints.strath.ac.uk/42646/</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>D. Neacsu, A. Salceanu, E. Lunca, V. David (2007). "Indirect Measurements on the Capacity in the Electrostatic HB Model". IMEKO TC4 Symposium, Iasi.</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>https://imeko.org/proceedings/indirect-measurements-on-the-capacity-in-the-electrostatic-hb-model</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>N. P. Dawkins, T. Yates, et al. (2022). "Normative wrist-worn accelerometer values for self-paced walking and running: a walk in the park". J. Sports Sciences.</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1080/02640414.2021.1976491</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>(authors as listed on arXiv) (2022). "A 'one-size-fits-most' walking recognition method for smartphones, smartwatches, and wearable accelerometers". arXiv:2207.07443.</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2207.07443</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>(authors not visible in the abstract) (2020). "Perturbation in public transport as a basic concept for perturbation-based balance training for fall prevention". Z. Gerontol. Geriatr..</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>https://link.springer.com/journal/391</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>J. Perry, J. M. Burnfield (2010). "Gait Analysis: Normal and Pathological Function, 2nd ed.". SLACK Inc..</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>https://www.healio.com/books</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>S. Krašna, et al. (2021). "Human Response to Longitudinal Perturbations of Standing Passengers on Public Transport During Regular Operation". Frontiers in Bioengineering and Biotechnology 9:680883.</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3389/fbioe.2021.680883</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Y. L. A. Kwok, J. Gralton, M.-L. McLaws (2015). "Face touching: a frequent habit that has implications for hand hygiene". American Journal of Infection Control 43(2):112-114.</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.ajic.2014.10.015</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>S. Mow, S. Seriani, T. Fujiyama (2024). "Where and how often do people touch train interiors? An investigation during the pandemic". Proc. ICE Municipal Engineer.</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>https://discovery.ucl.ac.uk/id/eprint/10199779/</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Bangalore Metro Rail Corporation Ltd. (n.d.). "Environmental Impact Assessment (design passenger loads)". BMRCL / JICA.</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jica.go.jp/</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Institute for Social and Economic Change (2019). "Determinants of intra-urban mobility: a study of Bengaluru (Working Paper 437)". ISEC.</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>https://ideas.repec.org/p/sch/wpaper/437.html</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Espressif Systems (n.d.). "ESP-FAQ: ADC". Espressif documentation.</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>https://docs.espressif.com/projects/esp-faq/</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>(Sen group, Purdue) (2024). "Step-to-Charge (EQS body powering)". arXiv:2408.01927.</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2408.01927</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>IEC (2008). "IEC 61000-4-2: Electrostatic discharge immunity test". International standard.</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>https://webstore.iec.ch/publication/4189</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>(Al-Quds / An-Najah University) (n.d.). "Residential exposure to ELF electric and magnetic fields in the city of Ramallah-Palestine". Journal article.</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>https://dspace.alquds.edu/items/bc4377ca-bfb7-4375-ab1a-435c8e020c57/full</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>O. Aziz, et al. (2017). "Validation of accuracy of SVM-based fall detection system using real-world fall and non-fall datasets". PLoS ONE 12(7):e0180318.</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0180318</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>M. Indraganti, et al. (2014). "Thermal insulation of Indian clothing ensembles (sari, salwar-kurti)". Windsor Conference.</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>https://architexturez.net/node/175314</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>B. B. Majumdar, et al. (BITS Pilani Hyderabad) (n.d.). "Harassment of women in public transport, Hyderabad". Transportation Research Record.</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/home/trr</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8133,6 +10882,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/SparshaGuard_paper_values.xlsx
+++ b/docs/SparshaGuard_paper_values.xlsx
@@ -9774,7 +9774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10847,6 +10847,42 @@
       </c>
       <c r="D59" s="8" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>K. Nabors, J. White (1991). "FastCap: A Multipole Accelerated 3-D Capacitance Extraction Program". IEEE Trans. Computer-Aided Design 10(11):1447-1459.</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/43.97624</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>H. Vogt, G. Atkinson, P. Nenzi (n.d.). "Ngspice User's Manual". ngspice project.</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>https://ngspice.sourceforge.io/docs.html</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10909,6 +10945,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
